--- a/jira_export_2026-06-29.xlsx
+++ b/jira_export_2026-06-29.xlsx
@@ -827,21 +827,21 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>728 h</t>
+          <t>737 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>932 h</t>
+          <t>920 h</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -857,7 +857,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1021 h</t>
+          <t>1007 h</t>
         </is>
       </c>
       <c r="B20" s="7" t="n"/>
@@ -1074,7 +1074,11 @@
           <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr"/>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
           <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
@@ -1109,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
@@ -1128,7 +1132,7 @@
         <v>3207.7</v>
       </c>
       <c r="P5" s="13" t="n">
-        <v>0</v>
+        <v>2138.47</v>
       </c>
     </row>
     <row r="6">
@@ -3453,7 +3457,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
@@ -3472,7 +3476,7 @@
         <v>1416</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>1132.8</v>
+        <v>809.14</v>
       </c>
     </row>
     <row r="39">
@@ -5013,7 +5017,7 @@
         <v>2</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
@@ -5032,7 +5036,7 @@
         <v>2560</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>1137.78</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="61">
@@ -7005,7 +7009,7 @@
         <v>4</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
@@ -7024,7 +7028,7 @@
         <v>1611.75</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>134.31</v>
+        <v>119.39</v>
       </c>
     </row>
     <row r="89">
@@ -7149,7 +7153,7 @@
         <v>4</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
@@ -8301,7 +8305,7 @@
         <v>5</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
@@ -8373,7 +8377,7 @@
         <v>5</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
@@ -8445,7 +8449,7 @@
         <v>5</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
@@ -11351,7 +11355,7 @@
         <v>15</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
@@ -14328,7 +14332,7 @@
         <v>67073.738</v>
       </c>
       <c r="P200" s="19" t="n">
-        <v>143.63</v>
+        <v>141.88</v>
       </c>
     </row>
   </sheetData>
@@ -15326,7 +15330,7 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>174 j</t>
+          <t>172 j</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15342,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>1021 h</t>
+          <t>1007 h</t>
         </is>
       </c>
     </row>
@@ -15379,7 +15383,7 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>346.5</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14">
@@ -15394,7 +15398,7 @@
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>92.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -15409,7 +15413,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="16"/>
@@ -15589,7 +15593,7 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>864.1900000000001</v>
+        <v>853.6900000000001</v>
       </c>
     </row>
     <row r="32">
@@ -15600,11 +15604,11 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="C32" s="15" t="n">
-        <v>92.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -15619,7 +15623,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>64.70999999999999</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -15710,7 +15714,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>254.5</v>
+        <v>258</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>57.75</v>
@@ -15719,17 +15723,17 @@
         <v>15.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>327.75</v>
+        <v>331.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>100</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>592.2</v>
+        <v>581.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -15740,7 +15744,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>121.5</v>
+        <v>123.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15749,7 +15753,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>136.5</v>
+        <v>138.75</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15.5</v>
@@ -15759,7 +15763,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15775,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -15856,16 +15860,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>387766</v>
+        <v>388730</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>190283</v>
+        <v>191697</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>197483</v>
+        <v>197033</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>160707</v>
+        <v>160257</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>18605</v>
@@ -15906,16 +15910,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>198811</v>
+        <v>199775</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>107991</v>
+        <v>109405</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>90820</v>
+        <v>90370</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>62963</v>
+        <v>62513</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>14535</v>
@@ -16014,22 +16018,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -16049,11 +16053,11 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -16509,22 +16513,22 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -16534,7 +16538,7 @@
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -16544,11 +16548,11 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="17">
@@ -16599,22 +16603,22 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -16627,39 +16631,35 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G18" s="12" t="inlineStr"/>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="I18" s="27" t="n">
-        <v>1775</v>
+        <v>32077</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -16672,25 +16672,29 @@
           <t>Migration</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr"/>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="I19" s="26" t="n">
-        <v>32077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -16700,7 +16704,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -16710,7 +16714,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -16720,7 +16724,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
@@ -16730,22 +16734,22 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -16755,7 +16759,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -16765,7 +16769,7 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
@@ -16775,22 +16779,22 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34054</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34045</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
@@ -16810,32 +16814,32 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170461</t>
         </is>
       </c>
       <c r="I22" s="27" t="n">
-        <v>3535</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34155</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -16855,32 +16859,32 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>00171080</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34054</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34045</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE NEUILLY SUR MARNE</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -16900,42 +16904,42 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00170461</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>4250</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34187</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -16945,32 +16949,32 @@
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>00171144</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="I25" s="26" t="n">
-        <v>0</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -16990,32 +16994,32 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="I26" s="27" t="n">
-        <v>1350</v>
+        <v>1095.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -17035,32 +17039,32 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="I27" s="26" t="n">
-        <v>1000</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -17080,32 +17084,32 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="I28" s="27" t="n">
-        <v>755</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -17125,32 +17129,32 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="I29" s="26" t="n">
-        <v>1840</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -17170,32 +17174,32 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="I30" s="27" t="n">
-        <v>6655</v>
+        <v>755</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -17215,32 +17219,32 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="I31" s="26" t="n">
-        <v>1890</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
@@ -17260,32 +17264,32 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="I32" s="27" t="n">
-        <v>1095.5</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -17298,35 +17302,39 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G33" s="15" t="inlineStr"/>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="I33" s="26" t="n">
-        <v>2625</v>
+        <v>895</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
@@ -17346,22 +17354,22 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="I34" s="27" t="n">
-        <v>895</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
@@ -17371,7 +17379,7 @@
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -17391,32 +17399,32 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="I35" s="26" t="n">
-        <v>2200</v>
+        <v>12429</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -17436,32 +17444,32 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="I36" s="27" t="n">
-        <v>12429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -17474,39 +17482,35 @@
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
+      <c r="G37" s="15" t="inlineStr"/>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="I37" s="26" t="n">
-        <v>2300</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
@@ -17526,11 +17530,11 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="I38" s="27" t="n">
-        <v>0</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="39">
@@ -17568,7 +17572,7 @@
       <c r="G40" s="18" t="n"/>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>14 commande(s)</t>
+          <t>13 commande(s)</t>
         </is>
       </c>
       <c r="I40" s="25" t="n">
@@ -17589,7 +17593,7 @@
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>20 commande(s)</t>
+          <t>21 commande(s)</t>
         </is>
       </c>
       <c r="I41" s="25" t="n">

--- a/jira_export_2026-06-29.xlsx
+++ b/jira_export_2026-06-29.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>67,074 €</t>
+          <t>67,488 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>22,779 €</t>
+          <t>23,194 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>737 h</t>
+          <t>743 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>2994.75</v>
+        <v>3194.4</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>1996.5</v>
+        <v>912.6900000000001</v>
       </c>
     </row>
     <row r="23">
@@ -7025,10 +7025,10 @@
         <v>2400</v>
       </c>
       <c r="O88" s="17" t="n">
-        <v>1611.75</v>
+        <v>1826.65</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>119.39</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="89">
@@ -8875,7 +8875,7 @@
         <v>7</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>7</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>680</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>453.33</v>
+        <v>272</v>
       </c>
     </row>
     <row r="116">
@@ -10609,7 +10609,7 @@
         <v>11</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>11</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>11</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>11</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>3121.2</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>2378.06</v>
+        <v>2269.96</v>
       </c>
     </row>
     <row r="143">
@@ -14329,10 +14329,10 @@
         <v>66535.84</v>
       </c>
       <c r="O200" s="19" t="n">
-        <v>67073.738</v>
+        <v>67488.288</v>
       </c>
       <c r="P200" s="19" t="n">
-        <v>141.88</v>
+        <v>141.48</v>
       </c>
     </row>
   </sheetData>
@@ -15714,7 +15714,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>258</v>
+        <v>260.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>57.75</v>
@@ -15723,17 +15723,17 @@
         <v>15.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>331.25</v>
+        <v>333.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>100</v>
+        <v>101.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>581.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15744,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>123.75</v>
+        <v>125.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15753,7 +15753,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>138.75</v>
+        <v>140.75</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>15.5</v>
@@ -15763,7 +15763,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>144</v>
+        <v>144.5</v>
       </c>
     </row>
   </sheetData>
@@ -15860,16 +15860,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>388730</v>
+        <v>395516</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>191697</v>
+        <v>196643</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>197033</v>
+        <v>198873</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>160257</v>
+        <v>162097</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>18605</v>
@@ -15885,16 +15885,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>188955</v>
+        <v>195741</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>82292</v>
+        <v>87238</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>106663</v>
+        <v>108503</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>97744</v>
+        <v>99584</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>4070</v>
@@ -16773,7 +16773,7 @@
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>0</v>
+        <v>1414.5</v>
       </c>
     </row>
     <row r="22">
@@ -17448,7 +17448,7 @@
         </is>
       </c>
       <c r="I36" s="27" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="37">
@@ -17555,7 +17555,7 @@
         </is>
       </c>
       <c r="I39" s="25" t="n">
-        <v>109496</v>
+        <v>118111</v>
       </c>
     </row>
     <row r="40">
@@ -17576,7 +17576,7 @@
         </is>
       </c>
       <c r="I40" s="25" t="n">
-        <v>35034</v>
+        <v>42234</v>
       </c>
     </row>
     <row r="41">
@@ -17597,7 +17597,7 @@
         </is>
       </c>
       <c r="I41" s="25" t="n">
-        <v>74462</v>
+        <v>75876</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-06-29.xlsx
+++ b/jira_export_2026-06-29.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>743 h</t>
+          <t>751 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -905,14 +905,14 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -928,7 +928,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>5</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
@@ -10506,7 +10506,11 @@
           <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
-      <c r="C138" s="15" t="inlineStr"/>
+      <c r="C138" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
           <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
@@ -10539,7 +10543,7 @@
         <v>11</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
@@ -12993,7 +12997,7 @@
         <v>33</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -14332,7 +14336,7 @@
         <v>67488.288</v>
       </c>
       <c r="P200" s="19" t="n">
-        <v>141.48</v>
+        <v>140.59</v>
       </c>
     </row>
   </sheetData>
@@ -15714,26 +15718,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>260.25</v>
+        <v>261.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>57.75</v>
+        <v>58.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>15.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>333.5</v>
+        <v>335.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>101.5</v>
+        <v>102.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>581.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15748,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>125.75</v>
+        <v>126.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15753,17 +15757,17 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>140.75</v>
+        <v>141.75</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>271.99</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15779,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>144.5</v>
+        <v>146.5</v>
       </c>
     </row>
   </sheetData>
@@ -15863,19 +15867,19 @@
         <v>395516</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>196643</v>
+        <v>197357</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>198873</v>
+        <v>198159</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>162097</v>
+        <v>163354</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>18605</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>18171</v>
+        <v>16200</v>
       </c>
     </row>
     <row r="6">
@@ -15913,19 +15917,19 @@
         <v>199775</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>109405</v>
+        <v>110119</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>90370</v>
+        <v>89656</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>62513</v>
+        <v>63770</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>14535</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>13322</v>
+        <v>11351</v>
       </c>
     </row>
   </sheetData>
@@ -17611,7 +17615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -17632,7 +17636,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>24 clôture(s) : 19 projet(s), 5 rework</t>
+          <t>25 clôture(s) : 19 projet(s), 6 rework</t>
         </is>
       </c>
     </row>
@@ -18332,17 +18336,17 @@
     <row r="27">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-23410</t>
+          <t>PDMDEP-14779</t>
         </is>
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+          <t>[ANTIBES] Réinstallation Littéralis base Test et Prod</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>[EVREUX PORTES DE NORMANDIE]</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -18356,66 +18360,96 @@
         </is>
       </c>
       <c r="F27" s="28" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="28" t="inlineStr">
         <is>
+          <t>PDMDEP-23410</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE] - Passage en prime</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>[EVREUX PORTES DE NORMANDIE]</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
           <t>PDMDEP-24216</t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F29" s="28" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n">
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="29" t="n"/>
-      <c r="E31" s="29" t="n"/>
-      <c r="F31" s="29" t="n">
-        <v>5</v>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="29" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-06-29.xlsx
+++ b/jira_export_2026-06-29.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>67,488 €</t>
+          <t>68,350 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>23,194 €</t>
+          <t>23,376 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>44,295 €</t>
+          <t>44,975 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>751 h</t>
+          <t>764 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>8.75</v>
+        <v>11.25</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         <v>910</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>1501.5</v>
+        <v>1683.5</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>171.6</v>
+        <v>149.64</v>
       </c>
     </row>
     <row r="74">
@@ -8233,7 +8233,7 @@
         <v>5</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>7</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>7</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
@@ -8963,10 +8963,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="13" t="n">
-        <v>680</v>
+        <v>1360</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>272</v>
+        <v>453.33</v>
       </c>
     </row>
     <row r="116">
@@ -9089,7 +9089,7 @@
         <v>7</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>415</v>
       </c>
       <c r="P117" s="13" t="n">
-        <v>92.22</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="118">
@@ -9161,7 +9161,7 @@
         <v>7</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>83.33</v>
+        <v>81.52</v>
       </c>
     </row>
     <row r="119">
@@ -9233,7 +9233,7 @@
         <v>7</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>7</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>7</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>11</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>11</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>11</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>11</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>11</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>3121.2</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>2269.96</v>
+        <v>2080.8</v>
       </c>
     </row>
     <row r="143">
@@ -11289,7 +11289,7 @@
         <v>15</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>18</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>33</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>18.25</v>
+        <v>18.5</v>
       </c>
       <c r="L173" s="12" t="inlineStr"/>
       <c r="M173" s="12" t="inlineStr"/>
@@ -14333,10 +14333,10 @@
         <v>66535.84</v>
       </c>
       <c r="O200" s="19" t="n">
-        <v>67488.288</v>
+        <v>68350.288</v>
       </c>
       <c r="P200" s="19" t="n">
-        <v>140.59</v>
+        <v>139.78</v>
       </c>
     </row>
   </sheetData>
@@ -15718,26 +15718,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>261.5</v>
+        <v>269.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>58.5</v>
+        <v>58.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>15.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>335.5</v>
+        <v>343.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>102.75</v>
+        <v>103.25</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>581.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -15748,7 +15748,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>126.75</v>
+        <v>127.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>14</v>
@@ -15757,7 +15757,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>141.75</v>
+        <v>142.75</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>17.5</v>
@@ -15767,7 +15767,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -15779,7 +15779,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>146.5</v>
+        <v>149.25</v>
       </c>
     </row>
   </sheetData>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>395516</v>
+        <v>394654</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>197357</v>
+        <v>196495</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>198159</v>
@@ -15889,10 +15889,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>195741</v>
+        <v>195559</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>87238</v>
+        <v>87056</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>108503</v>
@@ -15914,10 +15914,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>199775</v>
+        <v>199095</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>110119</v>
+        <v>109439</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>89656</v>

--- a/jira_export_2026-06-29.xlsx
+++ b/jira_export_2026-06-29.xlsx
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>83.0%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -9089,7 +9089,7 @@
         <v>7</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>415</v>
       </c>
       <c r="P117" s="13" t="n">
-        <v>90.22</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="118">
@@ -9161,7 +9161,7 @@
         <v>7</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>81.52</v>
+        <v>79.79000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -9233,7 +9233,7 @@
         <v>7</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>7</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>7</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>68350.288</v>
       </c>
       <c r="P200" s="19" t="n">
-        <v>139.78</v>
+        <v>139.63</v>
       </c>
     </row>
   </sheetData>
@@ -15718,7 +15718,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>269.25</v>
+        <v>269.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>58.75</v>
@@ -15727,7 +15727,7 @@
         <v>15.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>343.5</v>
+        <v>344</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>103.25</v>
@@ -15779,7 +15779,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>149.25</v>
+        <v>149.5</v>
       </c>
     </row>
   </sheetData>
@@ -15867,19 +15867,19 @@
         <v>394654</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>196495</v>
+        <v>197704</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>198159</v>
+        <v>196950</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>163354</v>
+        <v>168990</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>18605</v>
+        <v>12360</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>16200</v>
+        <v>15599</v>
       </c>
     </row>
     <row r="6">
@@ -15892,19 +15892,19 @@
         <v>195559</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>87056</v>
+        <v>88065</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>108503</v>
+        <v>107494</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>99584</v>
+        <v>99985</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>4070</v>
+        <v>3060</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4849</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="7">
@@ -15917,19 +15917,19 @@
         <v>199095</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>109439</v>
+        <v>109639</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>89656</v>
+        <v>89456</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>63770</v>
+        <v>69005</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>14535</v>
+        <v>9300</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>11351</v>
+        <v>11151</v>
       </c>
     </row>
   </sheetData>
